--- a/input/testDisco.xlsx
+++ b/input/testDisco.xlsx
@@ -15,7 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Aptos Narrow"/>
@@ -54,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -71,6 +73,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,7 +582,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:V3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22.83203125" customWidth="1" min="1" max="1"/>
     <col width="15.5" customWidth="1" min="2" max="2"/>
@@ -589,7 +593,7 @@
     <col width="14.5" customWidth="1" min="10" max="10"/>
     <col width="11.1640625" customWidth="1" min="12" max="12"/>
     <col width="14.1640625" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="33.33203125" customWidth="1" min="14" max="14"/>
     <col width="44.5" customWidth="1" min="15" max="15"/>
     <col width="12.83203125" customWidth="1" min="16" max="16"/>
     <col width="16.1640625" customWidth="1" min="17" max="17"/>
@@ -734,7 +738,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>DOWNLOADING</t>
+          <t>DOWNLOADED</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -748,6 +752,9 @@
           <t>Download</t>
         </is>
       </c>
+      <c r="K2" s="7" t="n">
+        <v>46180.19188388228</v>
+      </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Normalized</t>
@@ -755,10 +762,10 @@
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>./downloads</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="n"/>
+          <t>/Volumes/ADATA HD710/Downloads</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr"/>
       <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Evidence.com - Case Download Link</t>

--- a/input/testDisco.xlsx
+++ b/input/testDisco.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14120" yWindow="4580" windowWidth="44900" windowHeight="19220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-29940" yWindow="780" windowWidth="23040" windowHeight="12195" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -56,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -74,7 +74,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -85,53 +84,53 @@
       <alignment horizontal="general" vertical="center"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
       <alignment horizontal="general" vertical="center"/>
     </dxf>
     <dxf>
@@ -582,25 +581,25 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:V3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="22.83203125" customWidth="1" min="1" max="1"/>
-    <col width="15.5" customWidth="1" min="2" max="2"/>
+    <col width="22.85546875" customWidth="1" min="1" max="1"/>
+    <col width="15.42578125" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11.1640625" customWidth="1" min="4" max="4"/>
-    <col width="14.5" customWidth="1" min="5" max="6"/>
-    <col width="16.5" customWidth="1" min="7" max="7"/>
-    <col width="14.5" customWidth="1" min="10" max="10"/>
-    <col width="11.1640625" customWidth="1" min="12" max="12"/>
-    <col width="14.1640625" customWidth="1" min="13" max="13"/>
-    <col width="33.33203125" customWidth="1" min="14" max="14"/>
-    <col width="44.5" customWidth="1" min="15" max="15"/>
-    <col width="12.83203125" customWidth="1" min="16" max="16"/>
-    <col width="16.1640625" customWidth="1" min="17" max="17"/>
-    <col width="12.1640625" customWidth="1" min="18" max="18"/>
-    <col width="22.33203125" customWidth="1" min="20" max="20"/>
-    <col width="23.83203125" customWidth="1" min="21" max="21"/>
-    <col width="33.5" customWidth="1" min="22" max="22"/>
+    <col width="11.140625" customWidth="1" min="4" max="4"/>
+    <col width="14.42578125" customWidth="1" min="5" max="6"/>
+    <col width="16.42578125" customWidth="1" min="7" max="7"/>
+    <col width="14.42578125" customWidth="1" min="10" max="10"/>
+    <col width="11.140625" customWidth="1" min="12" max="12"/>
+    <col width="14.140625" customWidth="1" min="13" max="13"/>
+    <col width="33.28515625" customWidth="1" min="14" max="14"/>
+    <col width="44.42578125" customWidth="1" min="15" max="15"/>
+    <col width="12.85546875" customWidth="1" min="16" max="16"/>
+    <col width="16.140625" customWidth="1" min="17" max="17"/>
+    <col width="12.140625" customWidth="1" min="18" max="18"/>
+    <col width="22.28515625" customWidth="1" min="20" max="20"/>
+    <col width="23.85546875" customWidth="1" min="21" max="21"/>
+    <col width="33.42578125" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -715,7 +714,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40.75" customFormat="1" customHeight="1" s="1">
+    <row r="2" ht="40.7" customFormat="1" customHeight="1" s="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Odoms, Tameek</t>
@@ -752,8 +751,8 @@
           <t>Download</t>
         </is>
       </c>
-      <c r="K2" s="7" t="n">
-        <v>46180.19188388228</v>
+      <c r="K2" s="6" t="n">
+        <v>46180.28744148032</v>
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
@@ -762,7 +761,7 @@
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>/Volumes/ADATA HD710/Downloads</t>
+          <t>./downloads</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr"/>
